--- a/gradienteData/isotopes_gradiente_2023/weight_celulose_extraction.xlsx
+++ b/gradienteData/isotopes_gradiente_2023/weight_celulose_extraction.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://creaf-my.sharepoint.com/personal/p_fernandez_creaf_cat/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://creaf-my.sharepoint.com/personal/t_gimeno_creaf_uab_cat/Documents/terefi/repo/PHLISCOgradiente/gradienteData/isotopes_gradiente_2023/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{FFB3A8FD-32FF-4983-A961-05048A2F34C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2616BE2-1493-4924-AA85-53043B5AE350}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{FFB3A8FD-32FF-4983-A961-05048A2F34C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68B9FF5C-6CBE-4B18-AECC-FE266D45D951}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5548D504-3D1F-4935-8D67-2CC32DC927E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5548D504-3D1F-4935-8D67-2CC32DC927E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>Binary</t>
   </si>
@@ -288,6 +288,9 @@
   </si>
   <si>
     <t>Cellulose for isotopic analysis (mg)</t>
+  </si>
+  <si>
+    <t>Column1</t>
   </si>
 </sst>
 </file>
@@ -332,7 +335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -343,11 +346,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="20">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -398,21 +442,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{367814E9-DB04-423F-9064-863086F22EB9}" name="Table2" displayName="Table2" ref="A1:H43" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H43" xr:uid="{367814E9-DB04-423F-9064-863086F22EB9}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{5560C5DA-43C8-4636-BD1E-627C6D8D3072}" name="Binary" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{367814E9-DB04-423F-9064-863086F22EB9}" name="Table2" displayName="Table2" ref="A1:I44" totalsRowCount="1" headerRowDxfId="19" dataDxfId="18">
+  <autoFilter ref="A1:I43" xr:uid="{367814E9-DB04-423F-9064-863086F22EB9}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="MS_1_22"/>
+        <filter val="MS_1_23"/>
+        <filter val="MS_2_22"/>
+        <filter val="MS_2_23"/>
+        <filter val="MS_3_22"/>
+        <filter val="MS_3_23"/>
+        <filter val="MS_4_22"/>
+        <filter val="MS_4_23"/>
+        <filter val="MS_5_22"/>
+        <filter val="MS_5_23"/>
+        <filter val="MS_6_22"/>
+        <filter val="MS_6_23"/>
+        <filter val="MS_7_22"/>
+        <filter val="MS_7_23"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{5560C5DA-43C8-4636-BD1E-627C6D8D3072}" name="Binary" dataDxfId="17" totalsRowDxfId="8">
       <calculatedColumnFormula>DEC2BIN(Table2[[#This Row],[Order]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{149F0082-DEC1-4AFA-ACC4-764D3EFBA9B6}" name="Order" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{76EAF236-4578-47B6-953A-72C2B570BF9E}" name="Sample_ID" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{6F6F00EB-0A82-4FD5-A178-A12F2C5A8ED1}" name="Wood (mg)" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{F0024D7C-AD1F-423F-8224-99BEE0BF3399}" name="Cellulose (mg)" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{F34812F3-40D1-4C5D-A7B4-0019E39AD191}" name="Cellulose (%)" dataDxfId="2">
+    <tableColumn id="6" xr3:uid="{149F0082-DEC1-4AFA-ACC4-764D3EFBA9B6}" name="Order" dataDxfId="16" totalsRowDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{76EAF236-4578-47B6-953A-72C2B570BF9E}" name="Sample_ID" dataDxfId="15" totalsRowDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{6F6F00EB-0A82-4FD5-A178-A12F2C5A8ED1}" name="Wood (mg)" dataDxfId="14" totalsRowDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{F0024D7C-AD1F-423F-8224-99BEE0BF3399}" name="Cellulose (mg)" dataDxfId="13" totalsRowDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{F34812F3-40D1-4C5D-A7B4-0019E39AD191}" name="Cellulose (%)" totalsRowFunction="custom" dataDxfId="12" totalsRowDxfId="3">
       <calculatedColumnFormula>+Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]*100</calculatedColumnFormula>
+      <totalsRowFormula>(_xlfn.STDEV.P(F30,F31,F32,F33,F34,F35,F36,F37,F38,F39,F40,F41,F42,F43))/SQRT(14)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{B3499253-90AC-4847-92AA-104E2B7796B8}" name="Cellulose for isotopic analysis (mg)" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{EB6B1024-04FA-48E6-9D7B-568EF2E73C36}" name="Microplate position" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{B3499253-90AC-4847-92AA-104E2B7796B8}" name="Cellulose for isotopic analysis (mg)" dataDxfId="11" totalsRowDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{EB6B1024-04FA-48E6-9D7B-568EF2E73C36}" name="Microplate position" dataDxfId="10" totalsRowDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{2E9950E7-66DC-4374-9416-57B68B9CBD10}" name="Column1" dataDxfId="9" totalsRowDxfId="0">
+      <calculatedColumnFormula>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -738,19 +805,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="8.7265625" style="1"/>
-    <col min="3" max="3" width="11.81640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.90625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.90625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.90625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="8.7109375" style="1"/>
+    <col min="3" max="3" width="11.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -775,8 +842,11 @@
       <c r="H1" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -798,8 +868,12 @@
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -821,8 +895,12 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I3" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.35384615384615381</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>10</v>
       </c>
@@ -844,8 +922,12 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I4" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.24444444444444446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>11</v>
       </c>
@@ -867,8 +949,12 @@
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I5" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.32653061224489793</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>100</v>
       </c>
@@ -890,8 +976,12 @@
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I6" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>101</v>
       </c>
@@ -913,8 +1003,12 @@
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I7" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.36842105263157893</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>110</v>
       </c>
@@ -936,8 +1030,12 @@
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I8" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.2950819672131148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>111</v>
       </c>
@@ -959,8 +1057,12 @@
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I9" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.34883720930232559</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>81</v>
       </c>
@@ -982,8 +1084,12 @@
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I10" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.36231884057971014</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>80</v>
       </c>
@@ -1005,8 +1111,12 @@
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I11" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.34285714285714286</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>79</v>
       </c>
@@ -1028,8 +1138,12 @@
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I12" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.14814814814814814</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>78</v>
       </c>
@@ -1051,8 +1165,12 @@
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I13" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.36956521739130438</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>77</v>
       </c>
@@ -1074,8 +1192,12 @@
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I14" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.4081632653061224</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>76</v>
       </c>
@@ -1097,8 +1219,12 @@
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I15" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.39473684210526316</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>75</v>
       </c>
@@ -1120,8 +1246,12 @@
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I16" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.45454545454545453</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>74</v>
       </c>
@@ -1143,8 +1273,12 @@
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I17" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>73</v>
       </c>
@@ -1166,8 +1300,12 @@
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I18" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.35483870967741937</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>72</v>
       </c>
@@ -1189,8 +1327,12 @@
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I19" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.48979591836734687</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>71</v>
       </c>
@@ -1212,8 +1354,12 @@
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I20" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.47297297297297297</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>70</v>
       </c>
@@ -1235,8 +1381,12 @@
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I21" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.50704225352112675</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>69</v>
       </c>
@@ -1258,8 +1408,12 @@
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I22" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.48780487804878053</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>68</v>
       </c>
@@ -1281,8 +1435,12 @@
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I23" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.40625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>67</v>
       </c>
@@ -1304,8 +1462,12 @@
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I24" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.31521739130434784</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -1327,8 +1489,12 @@
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I25" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.40659340659340665</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>65</v>
       </c>
@@ -1350,8 +1516,12 @@
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I26" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.39560439560439564</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>64</v>
       </c>
@@ -1373,8 +1543,12 @@
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I27" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.32692307692307693</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>63</v>
       </c>
@@ -1396,8 +1570,12 @@
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I28" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.31428571428571433</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>62</v>
       </c>
@@ -1419,8 +1597,12 @@
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I29" s="2">
+        <f>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>61</v>
       </c>
@@ -1442,8 +1624,9 @@
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>60</v>
       </c>
@@ -1465,8 +1648,9 @@
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I31" s="2"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>59</v>
       </c>
@@ -1488,8 +1672,9 @@
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>58</v>
       </c>
@@ -1511,8 +1696,9 @@
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>57</v>
       </c>
@@ -1534,8 +1720,9 @@
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I34" s="2"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>56</v>
       </c>
@@ -1557,8 +1744,9 @@
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I35" s="2"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>55</v>
       </c>
@@ -1580,8 +1768,9 @@
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I36" s="2"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>54</v>
       </c>
@@ -1603,8 +1792,9 @@
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>53</v>
       </c>
@@ -1626,8 +1816,9 @@
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I38" s="2"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>52</v>
       </c>
@@ -1649,8 +1840,9 @@
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I39" s="2"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>51</v>
       </c>
@@ -1672,8 +1864,9 @@
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I40" s="2"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>50</v>
       </c>
@@ -1695,8 +1888,9 @@
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>49</v>
       </c>
@@ -1718,8 +1912,9 @@
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I42" s="2"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>48</v>
       </c>
@@ -1741,6 +1936,19 @@
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="4"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2">
+        <f>(_xlfn.STDEV.P(F30,F31,F32,F33,F34,F35,F36,F37,F38,F39,F40,F41,F42,F43))/SQRT(14)</f>
+        <v>1.4725198387123872</v>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1762,6 +1970,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010022A642A57D906E4BABB26AE63AD69356" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="4b8b1b7362e590b3257b297a739c41d7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7ea3dcc7-3087-49a9-bebf-dfe548a88604" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7046052237ede1ae3cfc80b3618a9d34" ns3:_="">
     <xsd:import namespace="7ea3dcc7-3087-49a9-bebf-dfe548a88604"/>
@@ -1905,12 +2119,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70EBFBDE-C893-4931-9A4F-F289F0ED3B40}">
   <ds:schemaRefs>
@@ -1920,6 +2128,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D8D348-A4DD-4C74-836C-0DA0310AE1EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7ea3dcc7-3087-49a9-bebf-dfe548a88604"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5C1D5C7-080D-4E81-B573-882A60A1C648}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1935,20 +2159,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D8D348-A4DD-4C74-836C-0DA0310AE1EC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7ea3dcc7-3087-49a9-bebf-dfe548a88604"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/gradienteData/isotopes_gradiente_2023/weight_celulose_extraction.xlsx
+++ b/gradienteData/isotopes_gradiente_2023/weight_celulose_extraction.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://creaf-my.sharepoint.com/personal/t_gimeno_creaf_uab_cat/Documents/terefi/repo/PHLISCOgradiente/gradienteData/isotopes_gradiente_2023/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{FFB3A8FD-32FF-4983-A961-05048A2F34C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68B9FF5C-6CBE-4B18-AECC-FE266D45D951}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{FFB3A8FD-32FF-4983-A961-05048A2F34C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0331B574-40EB-4584-8BF2-AEDCE080C9D1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5548D504-3D1F-4935-8D67-2CC32DC927E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{5548D504-3D1F-4935-8D67-2CC32DC927E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -335,7 +335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -345,9 +345,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -376,16 +373,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -419,7 +406,16 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -443,41 +439,22 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{367814E9-DB04-423F-9064-863086F22EB9}" name="Table2" displayName="Table2" ref="A1:I44" totalsRowCount="1" headerRowDxfId="19" dataDxfId="18">
-  <autoFilter ref="A1:I43" xr:uid="{367814E9-DB04-423F-9064-863086F22EB9}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="MS_1_22"/>
-        <filter val="MS_1_23"/>
-        <filter val="MS_2_22"/>
-        <filter val="MS_2_23"/>
-        <filter val="MS_3_22"/>
-        <filter val="MS_3_23"/>
-        <filter val="MS_4_22"/>
-        <filter val="MS_4_23"/>
-        <filter val="MS_5_22"/>
-        <filter val="MS_5_23"/>
-        <filter val="MS_6_22"/>
-        <filter val="MS_6_23"/>
-        <filter val="MS_7_22"/>
-        <filter val="MS_7_23"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I43" xr:uid="{367814E9-DB04-423F-9064-863086F22EB9}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{5560C5DA-43C8-4636-BD1E-627C6D8D3072}" name="Binary" dataDxfId="17" totalsRowDxfId="8">
+    <tableColumn id="1" xr3:uid="{5560C5DA-43C8-4636-BD1E-627C6D8D3072}" name="Binary" dataDxfId="16" totalsRowDxfId="17">
       <calculatedColumnFormula>DEC2BIN(Table2[[#This Row],[Order]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{149F0082-DEC1-4AFA-ACC4-764D3EFBA9B6}" name="Order" dataDxfId="16" totalsRowDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{76EAF236-4578-47B6-953A-72C2B570BF9E}" name="Sample_ID" dataDxfId="15" totalsRowDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{6F6F00EB-0A82-4FD5-A178-A12F2C5A8ED1}" name="Wood (mg)" dataDxfId="14" totalsRowDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{F0024D7C-AD1F-423F-8224-99BEE0BF3399}" name="Cellulose (mg)" dataDxfId="13" totalsRowDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{F34812F3-40D1-4C5D-A7B4-0019E39AD191}" name="Cellulose (%)" totalsRowFunction="custom" dataDxfId="12" totalsRowDxfId="3">
+    <tableColumn id="6" xr3:uid="{149F0082-DEC1-4AFA-ACC4-764D3EFBA9B6}" name="Order" dataDxfId="14" totalsRowDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{76EAF236-4578-47B6-953A-72C2B570BF9E}" name="Sample_ID" dataDxfId="12" totalsRowDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{6F6F00EB-0A82-4FD5-A178-A12F2C5A8ED1}" name="Wood (mg)" dataDxfId="10" totalsRowDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{F0024D7C-AD1F-423F-8224-99BEE0BF3399}" name="Cellulose (mg)" dataDxfId="8" totalsRowDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{F34812F3-40D1-4C5D-A7B4-0019E39AD191}" name="Cellulose (%)" totalsRowFunction="custom" dataDxfId="6" totalsRowDxfId="7">
       <calculatedColumnFormula>+Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]*100</calculatedColumnFormula>
-      <totalsRowFormula>(_xlfn.STDEV.P(F30,F31,F32,F33,F34,F35,F36,F37,F38,F39,F40,F41,F42,F43))/SQRT(14)</totalsRowFormula>
+      <totalsRowFormula>(_xlfn.STDEV.P(F2:F28,F36,F37,F38,F39,F40,F41,F42))/SQRT(37)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{B3499253-90AC-4847-92AA-104E2B7796B8}" name="Cellulose for isotopic analysis (mg)" dataDxfId="11" totalsRowDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{EB6B1024-04FA-48E6-9D7B-568EF2E73C36}" name="Microplate position" dataDxfId="10" totalsRowDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{2E9950E7-66DC-4374-9416-57B68B9CBD10}" name="Column1" dataDxfId="9" totalsRowDxfId="0">
+    <tableColumn id="7" xr3:uid="{B3499253-90AC-4847-92AA-104E2B7796B8}" name="Cellulose for isotopic analysis (mg)" dataDxfId="4" totalsRowDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{EB6B1024-04FA-48E6-9D7B-568EF2E73C36}" name="Microplate position" dataDxfId="2" totalsRowDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{2E9950E7-66DC-4374-9416-57B68B9CBD10}" name="Column1" dataDxfId="0" totalsRowDxfId="1">
       <calculatedColumnFormula>Table2[[#This Row],[Cellulose (mg)]]/Table2[[#This Row],[Wood (mg)]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -805,19 +782,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I45"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="2" width="8.7109375" style="1"/>
-    <col min="3" max="3" width="11.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="8.7265625" style="1"/>
+    <col min="3" max="3" width="11.86328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.86328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.86328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.26953125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.86328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="29.5" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -846,7 +823,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -873,7 +850,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -900,7 +877,7 @@
         <v>0.35384615384615381</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A4" s="1">
         <v>10</v>
       </c>
@@ -927,7 +904,7 @@
         <v>0.24444444444444446</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A5" s="1">
         <v>11</v>
       </c>
@@ -954,7 +931,7 @@
         <v>0.32653061224489793</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A6" s="1">
         <v>100</v>
       </c>
@@ -981,7 +958,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A7" s="1">
         <v>101</v>
       </c>
@@ -1008,7 +985,7 @@
         <v>0.36842105263157893</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A8" s="1">
         <v>110</v>
       </c>
@@ -1035,7 +1012,7 @@
         <v>0.2950819672131148</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A9" s="1">
         <v>111</v>
       </c>
@@ -1062,7 +1039,7 @@
         <v>0.34883720930232559</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
         <v>81</v>
       </c>
@@ -1089,7 +1066,7 @@
         <v>0.36231884057971014</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A11" s="1" t="s">
         <v>80</v>
       </c>
@@ -1116,7 +1093,7 @@
         <v>0.34285714285714286</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
         <v>79</v>
       </c>
@@ -1143,7 +1120,7 @@
         <v>0.14814814814814814</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A13" s="1" t="s">
         <v>78</v>
       </c>
@@ -1170,7 +1147,7 @@
         <v>0.36956521739130438</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A14" s="1" t="s">
         <v>77</v>
       </c>
@@ -1197,7 +1174,7 @@
         <v>0.4081632653061224</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A15" s="1" t="s">
         <v>76</v>
       </c>
@@ -1224,7 +1201,7 @@
         <v>0.39473684210526316</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A16" s="1" t="s">
         <v>75</v>
       </c>
@@ -1251,7 +1228,7 @@
         <v>0.45454545454545453</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A17" s="1" t="s">
         <v>74</v>
       </c>
@@ -1278,7 +1255,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A18" s="1" t="s">
         <v>73</v>
       </c>
@@ -1305,7 +1282,7 @@
         <v>0.35483870967741937</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A19" s="1" t="s">
         <v>72</v>
       </c>
@@ -1332,7 +1309,7 @@
         <v>0.48979591836734687</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A20" s="1" t="s">
         <v>71</v>
       </c>
@@ -1359,7 +1336,7 @@
         <v>0.47297297297297297</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A21" s="1" t="s">
         <v>70</v>
       </c>
@@ -1386,7 +1363,7 @@
         <v>0.50704225352112675</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A22" s="1" t="s">
         <v>69</v>
       </c>
@@ -1413,7 +1390,7 @@
         <v>0.48780487804878053</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A23" s="1" t="s">
         <v>68</v>
       </c>
@@ -1440,7 +1417,7 @@
         <v>0.40625</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A24" s="1" t="s">
         <v>67</v>
       </c>
@@ -1467,7 +1444,7 @@
         <v>0.31521739130434784</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -1494,7 +1471,7 @@
         <v>0.40659340659340665</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A26" s="1" t="s">
         <v>65</v>
       </c>
@@ -1521,7 +1498,7 @@
         <v>0.39560439560439564</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A27" s="1" t="s">
         <v>64</v>
       </c>
@@ -1548,7 +1525,7 @@
         <v>0.32692307692307693</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A28" s="1" t="s">
         <v>63</v>
       </c>
@@ -1575,7 +1552,7 @@
         <v>0.31428571428571433</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A29" s="1" t="s">
         <v>62</v>
       </c>
@@ -1602,7 +1579,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A30" s="1" t="s">
         <v>61</v>
       </c>
@@ -1626,7 +1603,7 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A31" s="1" t="s">
         <v>60</v>
       </c>
@@ -1650,7 +1627,7 @@
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A32" s="1" t="s">
         <v>59</v>
       </c>
@@ -1674,7 +1651,7 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A33" s="1" t="s">
         <v>58</v>
       </c>
@@ -1698,7 +1675,7 @@
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A34" s="1" t="s">
         <v>57</v>
       </c>
@@ -1722,7 +1699,7 @@
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A35" s="1" t="s">
         <v>56</v>
       </c>
@@ -1746,7 +1723,7 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A36" s="1" t="s">
         <v>55</v>
       </c>
@@ -1770,7 +1747,7 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A37" s="1" t="s">
         <v>54</v>
       </c>
@@ -1794,7 +1771,7 @@
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A38" s="1" t="s">
         <v>53</v>
       </c>
@@ -1818,7 +1795,7 @@
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A39" s="1" t="s">
         <v>52</v>
       </c>
@@ -1842,7 +1819,7 @@
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A40" s="1" t="s">
         <v>51</v>
       </c>
@@ -1866,7 +1843,7 @@
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A41" s="1" t="s">
         <v>50</v>
       </c>
@@ -1890,7 +1867,7 @@
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A42" s="1" t="s">
         <v>49</v>
       </c>
@@ -1914,7 +1891,7 @@
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A43" s="1" t="s">
         <v>48</v>
       </c>
@@ -1938,17 +1915,22 @@
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.75">
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2">
-        <f>(_xlfn.STDEV.P(F30,F31,F32,F33,F34,F35,F36,F37,F38,F39,F40,F41,F42,F43))/SQRT(14)</f>
-        <v>1.4725198387123872</v>
+        <f>(_xlfn.STDEV.P(F2:F28,F36,F37,F38,F39,F40,F41,F42))/SQRT(37)</f>
+        <v>1.1896128976659204</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.75">
+      <c r="F45" s="2">
+        <f>AVERAGE(F2:F28, F37:F43)</f>
+        <v>36.103074560112717</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1961,21 +1943,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010022A642A57D906E4BABB26AE63AD69356" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="4b8b1b7362e590b3257b297a739c41d7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7ea3dcc7-3087-49a9-bebf-dfe548a88604" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7046052237ede1ae3cfc80b3618a9d34" ns3:_="">
     <xsd:import namespace="7ea3dcc7-3087-49a9-bebf-dfe548a88604"/>
@@ -2119,10 +2086,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70EBFBDE-C893-4931-9A4F-F289F0ED3B40}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5C1D5C7-080D-4E81-B573-882A60A1C648}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7ea3dcc7-3087-49a9-bebf-dfe548a88604"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2144,19 +2136,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5C1D5C7-080D-4E81-B573-882A60A1C648}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70EBFBDE-C893-4931-9A4F-F289F0ED3B40}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7ea3dcc7-3087-49a9-bebf-dfe548a88604"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>